--- a/docs/次要装备榜.xlsx
+++ b/docs/次要装备榜.xlsx
@@ -13276,7 +13276,7 @@
       <c r="P3" s="5" t="n"/>
       <c r="Q3" s="6" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="R3" s="7" t="inlineStr">
@@ -13558,7 +13558,7 @@
       <c r="AB7" s="5" t="n"/>
       <c r="AC7" s="14" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="AD7" s="7" t="inlineStr">
@@ -14189,7 +14189,7 @@
       <c r="P19" s="5" t="n"/>
       <c r="Q19" s="14" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="R19" s="7" t="inlineStr">
@@ -14403,7 +14403,7 @@
       <c r="D23" s="5" t="n"/>
       <c r="E23" s="21" t="inlineStr">
         <is>
-          <t>D+</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
@@ -14420,7 +14420,7 @@
       <c r="J23" s="5" t="n"/>
       <c r="K23" s="19" t="inlineStr">
         <is>
-          <t>F+</t>
+          <t>F</t>
         </is>
       </c>
       <c r="L23" s="7" t="inlineStr">
@@ -14606,7 +14606,7 @@
       <c r="P27" s="5" t="n"/>
       <c r="Q27" s="8" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="R27" s="7" t="inlineStr">
@@ -14837,7 +14837,7 @@
       <c r="J31" s="5" t="n"/>
       <c r="K31" s="8" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L31" s="7" t="inlineStr">
@@ -14871,7 +14871,7 @@
       <c r="V31" s="5" t="n"/>
       <c r="W31" s="14" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X31" s="7" t="inlineStr">
@@ -15321,7 +15321,7 @@
       <c r="D39" s="5" t="n"/>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
@@ -15338,7 +15338,7 @@
       <c r="J39" s="5" t="n"/>
       <c r="K39" s="8" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L39" s="7" t="inlineStr">
@@ -15372,7 +15372,7 @@
       <c r="V39" s="5" t="n"/>
       <c r="W39" s="14" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X39" s="7" t="inlineStr">
@@ -15586,7 +15586,7 @@
       <c r="J43" s="5" t="n"/>
       <c r="K43" s="15" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L43" s="7" t="inlineStr">
@@ -15620,7 +15620,7 @@
       <c r="V43" s="5" t="n"/>
       <c r="W43" s="19" t="inlineStr">
         <is>
-          <t>F+</t>
+          <t>F</t>
         </is>
       </c>
       <c r="X43" s="7" t="inlineStr">
